--- a/grupos/2APM - Estadisticos 20212.xlsx
+++ b/grupos/2APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -167,24 +167,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,18 +203,93 @@
     <t>AVELLEIRA</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>YAIR DAVID</t>
+  </si>
+  <si>
+    <t>CRISTIAN MANUEL</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUZ AMELY</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -224,63 +299,33 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RICO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>XOCUA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>DELGADO</t>
   </si>
   <si>
@@ -290,54 +335,27 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
     <t>HIPOLITO</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
     <t>CASTELLANOS</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
     <t>DEBORA GEORGINA</t>
   </si>
   <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
     <t>GAEL JARED</t>
   </si>
   <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
     <t>CRISTINA KARELY</t>
   </si>
   <si>
@@ -347,30 +365,15 @@
     <t>DARLET VICTORIA</t>
   </si>
   <si>
-    <t>CRISTIAN MANUEL</t>
-  </si>
-  <si>
     <t>JONATHAN MOISES</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
     <t>JOCELIN</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
     <t>SAORI</t>
   </si>
   <si>
@@ -387,9 +390,6 @@
   </si>
   <si>
     <t>NOEMI</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
   <si>
     <t>PAULA MARIA</t>
@@ -906,13 +906,13 @@
         <v>-1</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G4">
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -969,13 +969,13 @@
         <v>-1</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -992,16 +992,16 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1055,16 +1055,16 @@
         <v>8</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1090,7 +1090,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1153,7 +1153,7 @@
         <v>6</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1173,13 +1173,13 @@
         <v>-1</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1236,13 +1236,13 @@
         <v>-1</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>9</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1259,16 +1259,16 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1322,16 +1322,16 @@
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1351,13 +1351,13 @@
         <v>-1</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1414,13 +1414,13 @@
         <v>-1</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1440,13 +1440,13 @@
         <v>-1</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1503,13 +1503,13 @@
         <v>-1</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1526,16 +1526,16 @@
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1589,16 +1589,16 @@
         <v>8</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1615,16 +1615,16 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1678,16 +1678,16 @@
         <v>9</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB12">
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1704,16 +1704,16 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1767,16 +1767,16 @@
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1796,13 +1796,13 @@
         <v>-1</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1859,13 +1859,13 @@
         <v>-1</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1882,16 +1882,16 @@
         <v>7</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1945,16 +1945,16 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>9</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1971,16 +1971,16 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2034,16 +2034,16 @@
         <v>9</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB16">
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2060,16 +2060,16 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2123,16 +2123,16 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2149,16 +2149,16 @@
         <v>8</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2212,16 +2212,16 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2238,16 +2238,16 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2301,16 +2301,16 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>9</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2330,13 +2330,13 @@
         <v>-1</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2393,13 +2393,13 @@
         <v>-1</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB20">
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2419,13 +2419,13 @@
         <v>-1</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2482,13 +2482,13 @@
         <v>-1</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2505,16 +2505,16 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2568,16 +2568,16 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>8</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2594,16 +2594,16 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G23">
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2657,16 +2657,16 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2683,16 +2683,16 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2746,16 +2746,16 @@
         <v>6</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2772,16 +2772,16 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2835,16 +2835,16 @@
         <v>9</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB25">
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2861,16 +2861,16 @@
         <v>9</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2924,16 +2924,16 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB26">
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2950,16 +2950,16 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3013,16 +3013,16 @@
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3039,16 +3039,16 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3102,16 +3102,16 @@
         <v>8</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3131,13 +3131,13 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>-1</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3194,13 +3194,13 @@
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>-1</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3217,16 +3217,16 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3280,16 +3280,16 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3354,27 +3354,30 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.9</v>
+      </c>
       <c r="I2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -3383,88 +3386,94 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>70.37</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7.5</v>
+      </c>
       <c r="I3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>27</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
       <c r="I4">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>27</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>85.19</v>
+      </c>
+      <c r="G5">
+        <v>14.81</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>70.37</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.5</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>29.63</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
@@ -3473,30 +3482,30 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>77.78</v>
+        <v>96.3</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>22.22</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3505,30 +3514,30 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>85.19</v>
+        <v>96.3</v>
       </c>
       <c r="G7">
-        <v>14.81</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
@@ -3537,25 +3546,25 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3565,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3600,13 +3609,13 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
@@ -3620,13 +3629,13 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>50</v>
@@ -3640,56 +3649,56 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920331</v>
+        <v>21330051920332</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920331</v>
+        <v>21330051920332</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3700,16 +3709,16 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3720,13 +3729,13 @@
         <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>50</v>
@@ -3734,79 +3743,79 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920332</v>
+        <v>21330051920334</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920332</v>
+        <v>21330051920334</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920332</v>
+        <v>21330051920334</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920333</v>
+        <v>21330051920335</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>49</v>
@@ -3814,79 +3823,79 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920333</v>
+        <v>21330051920336</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920333</v>
+        <v>21330051920341</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920334</v>
+        <v>21330051920341</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920334</v>
+        <v>21330051920343</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
         <v>50</v>
@@ -3894,79 +3903,79 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920334</v>
+        <v>21330051920347</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920334</v>
+        <v>21330051920347</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920334</v>
+        <v>21330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920335</v>
+        <v>21330051920348</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
         <v>86</v>
       </c>
-      <c r="D20" t="s">
-        <v>103</v>
-      </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>49</v>
@@ -3974,19 +3983,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920335</v>
+        <v>21330051920348</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
         <v>86</v>
       </c>
-      <c r="D21" t="s">
-        <v>103</v>
-      </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>50</v>
@@ -3994,1522 +4003,102 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920335</v>
+        <v>21330051920149</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920137</v>
+        <v>21330051920353</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920137</v>
+        <v>21330051920353</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920137</v>
+        <v>21330051920353</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920336</v>
+        <v>21330051920353</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920336</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920336</v>
-      </c>
-      <c r="B28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920338</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920338</v>
-      </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920338</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920339</v>
-      </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920339</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920339</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920340</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920340</v>
-      </c>
-      <c r="B36" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920340</v>
-      </c>
-      <c r="B37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920341</v>
-      </c>
-      <c r="B38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920341</v>
-      </c>
-      <c r="B39" t="s">
-        <v>68</v>
-      </c>
-      <c r="C39" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920341</v>
-      </c>
-      <c r="B40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C40" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920341</v>
-      </c>
-      <c r="B41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" t="s">
-        <v>71</v>
-      </c>
-      <c r="D41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920342</v>
-      </c>
-      <c r="B42" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920342</v>
-      </c>
-      <c r="B43" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D43" t="s">
-        <v>110</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920342</v>
-      </c>
-      <c r="B44" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920343</v>
-      </c>
-      <c r="B45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" t="s">
-        <v>76</v>
-      </c>
-      <c r="D45" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920343</v>
-      </c>
-      <c r="B46" t="s">
-        <v>69</v>
-      </c>
-      <c r="C46" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920343</v>
-      </c>
-      <c r="B47" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D47" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920343</v>
-      </c>
-      <c r="B48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" t="s">
-        <v>111</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920344</v>
-      </c>
-      <c r="B49" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D49" t="s">
-        <v>112</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920344</v>
-      </c>
-      <c r="B50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" t="s">
-        <v>112</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920344</v>
-      </c>
-      <c r="B51" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51" t="s">
-        <v>112</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920345</v>
-      </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" t="s">
-        <v>88</v>
-      </c>
-      <c r="D52" t="s">
-        <v>113</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920345</v>
-      </c>
-      <c r="B53" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" t="s">
-        <v>88</v>
-      </c>
-      <c r="D53" t="s">
-        <v>113</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920345</v>
-      </c>
-      <c r="B54" t="s">
-        <v>71</v>
-      </c>
-      <c r="C54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" t="s">
-        <v>113</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920346</v>
-      </c>
-      <c r="B55" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" t="s">
-        <v>114</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920346</v>
-      </c>
-      <c r="B56" t="s">
-        <v>72</v>
-      </c>
-      <c r="C56" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920346</v>
-      </c>
-      <c r="B57" t="s">
-        <v>72</v>
-      </c>
-      <c r="C57" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" t="s">
-        <v>114</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920347</v>
-      </c>
-      <c r="B58" t="s">
-        <v>73</v>
-      </c>
-      <c r="C58" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" t="s">
-        <v>115</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920347</v>
-      </c>
-      <c r="B59" t="s">
-        <v>73</v>
-      </c>
-      <c r="C59" t="s">
-        <v>90</v>
-      </c>
-      <c r="D59" t="s">
-        <v>115</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920347</v>
-      </c>
-      <c r="B60" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" t="s">
-        <v>115</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920347</v>
-      </c>
-      <c r="B61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" t="s">
-        <v>115</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920347</v>
-      </c>
-      <c r="B62" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" t="s">
-        <v>115</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920348</v>
-      </c>
-      <c r="B63" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63" t="s">
-        <v>116</v>
-      </c>
-      <c r="E63" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920348</v>
-      </c>
-      <c r="B64" t="s">
-        <v>73</v>
-      </c>
-      <c r="C64" t="s">
-        <v>91</v>
-      </c>
-      <c r="D64" t="s">
-        <v>116</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920348</v>
-      </c>
-      <c r="B65" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" t="s">
-        <v>91</v>
-      </c>
-      <c r="D65" t="s">
-        <v>116</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920348</v>
-      </c>
-      <c r="B66" t="s">
-        <v>73</v>
-      </c>
-      <c r="C66" t="s">
-        <v>91</v>
-      </c>
-      <c r="D66" t="s">
-        <v>116</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920349</v>
-      </c>
-      <c r="B67" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" t="s">
-        <v>92</v>
-      </c>
-      <c r="D67" t="s">
-        <v>117</v>
-      </c>
-      <c r="E67" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920349</v>
-      </c>
-      <c r="B68" t="s">
-        <v>74</v>
-      </c>
-      <c r="C68" t="s">
-        <v>92</v>
-      </c>
-      <c r="D68" t="s">
-        <v>117</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920349</v>
-      </c>
-      <c r="B69" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" t="s">
-        <v>92</v>
-      </c>
-      <c r="D69" t="s">
-        <v>117</v>
-      </c>
-      <c r="E69" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920350</v>
-      </c>
-      <c r="B70" t="s">
-        <v>75</v>
-      </c>
-      <c r="C70" t="s">
-        <v>93</v>
-      </c>
-      <c r="D70" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920350</v>
-      </c>
-      <c r="B71" t="s">
-        <v>75</v>
-      </c>
-      <c r="C71" t="s">
-        <v>93</v>
-      </c>
-      <c r="D71" t="s">
-        <v>118</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920350</v>
-      </c>
-      <c r="B72" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" t="s">
-        <v>93</v>
-      </c>
-      <c r="D72" t="s">
-        <v>118</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920149</v>
-      </c>
-      <c r="B73" t="s">
-        <v>76</v>
-      </c>
-      <c r="C73" t="s">
-        <v>94</v>
-      </c>
-      <c r="D73" t="s">
-        <v>112</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920149</v>
-      </c>
-      <c r="B74" t="s">
-        <v>76</v>
-      </c>
-      <c r="C74" t="s">
-        <v>94</v>
-      </c>
-      <c r="D74" t="s">
-        <v>112</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920149</v>
-      </c>
-      <c r="B75" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>94</v>
-      </c>
-      <c r="D75" t="s">
-        <v>112</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920149</v>
-      </c>
-      <c r="B76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C76" t="s">
-        <v>94</v>
-      </c>
-      <c r="D76" t="s">
-        <v>112</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920351</v>
-      </c>
-      <c r="B77" t="s">
-        <v>77</v>
-      </c>
-      <c r="C77" t="s">
-        <v>94</v>
-      </c>
-      <c r="D77" t="s">
-        <v>119</v>
-      </c>
-      <c r="E77" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920351</v>
-      </c>
-      <c r="B78" t="s">
-        <v>77</v>
-      </c>
-      <c r="C78" t="s">
-        <v>94</v>
-      </c>
-      <c r="D78" t="s">
-        <v>119</v>
-      </c>
-      <c r="E78" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920351</v>
-      </c>
-      <c r="B79" t="s">
-        <v>77</v>
-      </c>
-      <c r="C79" t="s">
-        <v>94</v>
-      </c>
-      <c r="D79" t="s">
-        <v>119</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920322</v>
-      </c>
-      <c r="B80" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80" t="s">
-        <v>120</v>
-      </c>
-      <c r="E80" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920322</v>
-      </c>
-      <c r="B81" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81" t="s">
-        <v>95</v>
-      </c>
-      <c r="D81" t="s">
-        <v>120</v>
-      </c>
-      <c r="E81" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920322</v>
-      </c>
-      <c r="B82" t="s">
-        <v>78</v>
-      </c>
-      <c r="C82" t="s">
-        <v>95</v>
-      </c>
-      <c r="D82" t="s">
-        <v>120</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920174</v>
-      </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" t="s">
-        <v>94</v>
-      </c>
-      <c r="D83" t="s">
-        <v>121</v>
-      </c>
-      <c r="E83" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920174</v>
-      </c>
-      <c r="B84" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" t="s">
-        <v>94</v>
-      </c>
-      <c r="D84" t="s">
-        <v>121</v>
-      </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920174</v>
-      </c>
-      <c r="B85" t="s">
-        <v>79</v>
-      </c>
-      <c r="C85" t="s">
-        <v>94</v>
-      </c>
-      <c r="D85" t="s">
-        <v>121</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920352</v>
-      </c>
-      <c r="B86" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" t="s">
-        <v>96</v>
-      </c>
-      <c r="D86" t="s">
-        <v>122</v>
-      </c>
-      <c r="E86" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920352</v>
-      </c>
-      <c r="B87" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" t="s">
-        <v>96</v>
-      </c>
-      <c r="D87" t="s">
-        <v>122</v>
-      </c>
-      <c r="E87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920352</v>
-      </c>
-      <c r="B88" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88" t="s">
-        <v>96</v>
-      </c>
-      <c r="D88" t="s">
-        <v>122</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920353</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89" t="s">
-        <v>123</v>
-      </c>
-      <c r="E89" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920353</v>
-      </c>
-      <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" t="s">
-        <v>97</v>
-      </c>
-      <c r="D90" t="s">
-        <v>123</v>
-      </c>
-      <c r="E90" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920353</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" t="s">
-        <v>97</v>
-      </c>
-      <c r="D91" t="s">
-        <v>123</v>
-      </c>
-      <c r="E91" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920353</v>
-      </c>
-      <c r="B92" t="s">
-        <v>81</v>
-      </c>
-      <c r="C92" t="s">
-        <v>97</v>
-      </c>
-      <c r="D92" t="s">
-        <v>123</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920353</v>
-      </c>
-      <c r="B93" t="s">
-        <v>81</v>
-      </c>
-      <c r="C93" t="s">
-        <v>97</v>
-      </c>
-      <c r="D93" t="s">
-        <v>123</v>
-      </c>
-      <c r="E93" t="s">
-        <v>6</v>
-      </c>
-      <c r="F93" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920353</v>
-      </c>
-      <c r="B94" t="s">
-        <v>81</v>
-      </c>
-      <c r="C94" t="s">
-        <v>97</v>
-      </c>
-      <c r="D94" t="s">
-        <v>123</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920354</v>
-      </c>
-      <c r="B95" t="s">
-        <v>82</v>
-      </c>
-      <c r="C95" t="s">
-        <v>98</v>
-      </c>
-      <c r="D95" t="s">
-        <v>124</v>
-      </c>
-      <c r="E95" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920354</v>
-      </c>
-      <c r="B96" t="s">
-        <v>82</v>
-      </c>
-      <c r="C96" t="s">
-        <v>98</v>
-      </c>
-      <c r="D96" t="s">
-        <v>124</v>
-      </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920354</v>
-      </c>
-      <c r="B97" t="s">
-        <v>82</v>
-      </c>
-      <c r="C97" t="s">
-        <v>98</v>
-      </c>
-      <c r="D97" t="s">
-        <v>124</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -5545,53 +4134,53 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920353</v>
+        <v>21330051920332</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920332</v>
+        <v>21330051920331</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5599,16 +4188,16 @@
         <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5616,16 +4205,16 @@
         <v>21330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5633,135 +4222,135 @@
         <v>21330051920341</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920343</v>
+        <v>21330051920348</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920348</v>
+        <v>21330051920335</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920149</v>
+        <v>21330051920336</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920333</v>
+        <v>21330051920343</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920335</v>
+        <v>21330051920149</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920137</v>
+        <v>21330051920333</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920336</v>
+        <v>21330051920137</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5769,16 +4358,16 @@
         <v>21330051920338</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5786,16 +4375,16 @@
         <v>21330051920339</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5803,16 +4392,16 @@
         <v>21330051920340</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5820,16 +4409,16 @@
         <v>21330051920342</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5837,16 +4426,16 @@
         <v>21330051920344</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5854,16 +4443,16 @@
         <v>21330051920345</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5871,16 +4460,16 @@
         <v>21330051920346</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5888,16 +4477,16 @@
         <v>21330051920349</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5905,16 +4494,16 @@
         <v>21330051920350</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5922,16 +4511,16 @@
         <v>21330051920351</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5939,16 +4528,16 @@
         <v>21330051920322</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5956,16 +4545,16 @@
         <v>21330051920174</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5973,16 +4562,16 @@
         <v>21330051920352</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5990,16 +4579,16 @@
         <v>21330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>124</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6009,7 +4598,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6039,6 +4628,213 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920341</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920341</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920348</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920348</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920335</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920336</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920343</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920345</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920149</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2APM - Estadisticos 20212.xlsx
+++ b/grupos/2APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -170,21 +170,21 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>Morales Vallejo Jorge Luis</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,157 +215,157 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>NAHOMI ITZAYANA</t>
+  </si>
+  <si>
+    <t>YAIR DAVID</t>
+  </si>
+  <si>
+    <t>CRISTIAN MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LUZ AMELY</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JOSUE EDUARDO</t>
-  </si>
-  <si>
-    <t>NAHOMI ITZAYANA</t>
-  </si>
-  <si>
-    <t>YAIR DAVID</t>
-  </si>
-  <si>
-    <t>CRISTIAN MANUEL</t>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>DEBORA GEORGINA</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>CRISTINA KARELY</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>DARLET VICTORIA</t>
+  </si>
+  <si>
+    <t>JONATHAN MOISES</t>
   </si>
   <si>
     <t>ROBERTO</t>
   </si>
   <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>LUZ AMELY</t>
-  </si>
-  <si>
     <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>DEBORA GEORGINA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>CRISTINA KARELY</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DARLET VICTORIA</t>
-  </si>
-  <si>
-    <t>JONATHAN MOISES</t>
   </si>
   <si>
     <t>JOCELIN</t>
@@ -927,10 +927,10 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1004,22 +1004,22 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1046,7 +1046,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>9</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1105,10 +1105,10 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1147,10 +1147,10 @@
         <v>-1</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1164,10 +1164,10 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1185,19 +1185,19 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1227,19 +1227,19 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>-1</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>7</v>
@@ -1271,22 +1271,22 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1316,10 +1316,10 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>6</v>
@@ -1360,22 +1360,22 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1402,10 +1402,10 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1452,16 +1452,16 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1503,7 +1503,7 @@
         <v>-1</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1538,22 +1538,22 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1583,10 +1583,10 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1595,7 +1595,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1627,22 +1627,22 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1669,13 +1669,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1716,22 +1716,22 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1761,10 +1761,10 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>7</v>
@@ -1790,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>-1</v>
@@ -1805,22 +1805,22 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1850,10 +1850,10 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>-1</v>
@@ -1894,22 +1894,22 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1939,16 +1939,16 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>9</v>
@@ -1965,7 +1965,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -1986,19 +1986,19 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2028,7 +2028,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -2072,22 +2072,22 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2114,13 +2114,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -2129,7 +2129,7 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -2161,22 +2161,22 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2203,10 +2203,10 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>9</v>
@@ -2250,22 +2250,22 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2307,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2321,10 +2321,10 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>-1</v>
@@ -2345,16 +2345,16 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2384,10 +2384,10 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>-1</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2410,7 +2410,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2431,19 +2431,19 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2473,7 +2473,7 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2485,7 +2485,7 @@
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2520,19 +2520,19 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2574,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2606,22 +2606,22 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2648,22 +2648,22 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -2677,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2701,16 +2701,16 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2740,7 +2740,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2749,7 +2749,7 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -2784,22 +2784,22 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2829,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2873,22 +2873,22 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2918,10 +2918,10 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>7</v>
@@ -2962,22 +2962,22 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -3007,10 +3007,10 @@
         <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z27">
         <v>8</v>
@@ -3051,22 +3051,22 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3093,10 +3093,10 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>-1</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>-1</v>
@@ -3134,7 +3134,7 @@
         <v>6</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -3146,13 +3146,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3188,16 +3188,16 @@
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>6</v>
@@ -3229,22 +3229,22 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3274,10 +3274,10 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
         <v>9</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -3386,62 +3386,62 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>88.89</v>
+      </c>
+      <c r="G3">
+        <v>11.11</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>70.37</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.5</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>29.63</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>27</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -3450,25 +3450,25 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>85.19</v>
+        <v>92.59</v>
       </c>
       <c r="G5">
-        <v>14.81</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3485,27 +3485,27 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>96.3</v>
       </c>
       <c r="G6">
+        <v>3.7</v>
+      </c>
+      <c r="H6">
+        <v>8.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3514,30 +3514,30 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3574,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3609,10 +3609,10 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -3629,16 +3629,16 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3649,16 +3649,16 @@
         <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3669,16 +3669,16 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3689,16 +3689,16 @@
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3709,50 +3709,50 @@
         <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920332</v>
+        <v>21330051920334</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920334</v>
+        <v>21330051920335</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -3763,30 +3763,30 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920334</v>
+        <v>21330051920336</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920334</v>
+        <v>21330051920341</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
         <v>71</v>
@@ -3795,18 +3795,18 @@
         <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920335</v>
+        <v>21330051920347</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
         <v>72</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920336</v>
+        <v>21330051920348</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -3843,13 +3843,13 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920341</v>
+        <v>21330051920353</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>83</v>
@@ -3863,242 +3863,22 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920341</v>
+        <v>21330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
         <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920343</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920347</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920347</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920347</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920348</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920348</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920149</v>
-      </c>
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920353</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920353</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920353</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920353</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -4134,53 +3914,53 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920332</v>
+        <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920353</v>
+        <v>21330051920332</v>
       </c>
       <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
         <v>68</v>
       </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920331</v>
+        <v>21330051920353</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4191,72 +3971,72 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920347</v>
+        <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920341</v>
+        <v>21330051920336</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920348</v>
+        <v>21330051920341</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920335</v>
+        <v>21330051920347</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -4270,10 +4050,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920336</v>
+        <v>21330051920348</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
@@ -4287,47 +4067,47 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920343</v>
+        <v>21330051920333</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920149</v>
+        <v>21330051920137</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920333</v>
+        <v>21330051920338</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
         <v>110</v>
@@ -4338,13 +4118,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920137</v>
+        <v>21330051920339</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>111</v>
@@ -4355,13 +4135,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920338</v>
+        <v>21330051920340</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
@@ -4372,13 +4152,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920339</v>
+        <v>21330051920342</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
         <v>113</v>
@@ -4389,13 +4169,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920340</v>
+        <v>21330051920343</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
         <v>114</v>
@@ -4406,13 +4186,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920342</v>
+        <v>21330051920344</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>115</v>
@@ -4423,16 +4203,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920344</v>
+        <v>21330051920345</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4440,16 +4220,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920345</v>
+        <v>21330051920346</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4457,16 +4237,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920346</v>
+        <v>21330051920349</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4474,16 +4254,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920349</v>
+        <v>21330051920350</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4491,16 +4271,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920350</v>
+        <v>21330051920149</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4511,10 +4291,10 @@
         <v>21330051920351</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>120</v>
@@ -4528,10 +4308,10 @@
         <v>21330051920322</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>121</v>
@@ -4545,10 +4325,10 @@
         <v>21330051920174</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
         <v>122</v>
@@ -4562,10 +4342,10 @@
         <v>21330051920352</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
         <v>123</v>
@@ -4579,10 +4359,10 @@
         <v>21330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>124</v>
@@ -4598,7 +4378,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4630,22 +4410,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920341</v>
+        <v>21330051920334</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4653,16 +4433,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920341</v>
+        <v>21330051920335</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4676,22 +4456,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920348</v>
+        <v>21330051920336</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4699,16 +4479,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920348</v>
+        <v>21330051920341</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4722,10 +4502,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920335</v>
+        <v>21330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>72</v>
@@ -4745,10 +4525,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920336</v>
+        <v>21330051920348</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>73</v>
@@ -4763,75 +4543,6 @@
         <v>49</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920343</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920345</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920149</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20212.xlsx
+++ b/grupos/2APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -203,6 +203,21 @@
     <t>AVELLEIRA</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>MARITZA</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
@@ -212,28 +227,73 @@
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>JUAREZ</t>
@@ -242,13 +302,28 @@
     <t>VELASCO</t>
   </si>
   <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>MARITZA</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>DEBORA GEORGINA</t>
   </si>
   <si>
     <t>JOSUE EDUARDO</t>
@@ -257,139 +332,64 @@
     <t>NAHOMI ITZAYANA</t>
   </si>
   <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
     <t>YAIR DAVID</t>
   </si>
   <si>
+    <t>CRISTINA KARELY</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>DARLET VICTORIA</t>
+  </si>
+  <si>
     <t>CRISTIAN MANUEL</t>
   </si>
   <si>
+    <t>JONATHAN MOISES</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>JOCELIN</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
     <t>LUZ AMELY</t>
   </si>
   <si>
+    <t>SAORI</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>AMIR ALONSO</t>
+  </si>
+  <si>
+    <t>GEMMA MARIA</t>
+  </si>
+  <si>
+    <t>EYTHAN</t>
+  </si>
+  <si>
+    <t>NOEMI</t>
+  </si>
+  <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>DEBORA GEORGINA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>CRISTINA KARELY</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>DARLET VICTORIA</t>
-  </si>
-  <si>
-    <t>JONATHAN MOISES</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>JOCELIN</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>SAORI</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>AMIR ALONSO</t>
-  </si>
-  <si>
-    <t>GEMMA MARIA</t>
-  </si>
-  <si>
-    <t>EYTHAN</t>
-  </si>
-  <si>
-    <t>NOEMI</t>
   </si>
   <si>
     <t>PAULA MARIA</t>
@@ -903,7 +903,7 @@
         <v>-1</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -915,7 +915,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -924,7 +924,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -966,7 +966,7 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -975,7 +975,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1013,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -1022,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1055,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>-1</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -1102,7 +1102,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1111,7 +1111,7 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1144,7 +1144,7 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>7</v>
@@ -1153,7 +1153,7 @@
         <v>5</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1170,7 +1170,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>7</v>
@@ -1182,7 +1182,7 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -1191,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1200,7 +1200,7 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1224,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1233,7 +1233,7 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1280,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1289,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1322,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1348,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1378,7 +1378,7 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1411,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -1449,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>7</v>
@@ -1458,7 +1458,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1467,7 +1467,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1491,7 +1491,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1500,7 +1500,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1509,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1547,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>9</v>
@@ -1556,7 +1556,7 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1636,7 +1636,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1645,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1725,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1734,7 +1734,7 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1776,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1793,7 +1793,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>8</v>
@@ -1814,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1823,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1856,7 +1856,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1912,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1983,7 +1983,7 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1992,7 +1992,7 @@
         <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -2001,7 +2001,7 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2025,7 +2025,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -2081,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -2090,7 +2090,7 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2123,7 +2123,7 @@
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2170,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2179,7 +2179,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2212,7 +2212,7 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2268,7 +2268,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2301,7 +2301,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2327,7 +2327,7 @@
         <v>6</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>7</v>
@@ -2339,16 +2339,16 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2399,7 +2399,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2416,7 +2416,7 @@
         <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>10</v>
@@ -2428,7 +2428,7 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -2437,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2479,7 +2479,7 @@
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>10</v>
@@ -2517,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>8</v>
@@ -2526,7 +2526,7 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2535,7 +2535,7 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2568,7 +2568,7 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>8</v>
@@ -2615,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2624,7 +2624,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2695,16 +2695,16 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2737,7 +2737,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2755,7 +2755,7 @@
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2793,7 +2793,7 @@
         <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2802,7 +2802,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2835,7 +2835,7 @@
         <v>9</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2882,7 +2882,7 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2891,7 +2891,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2924,7 +2924,7 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>10</v>
@@ -2971,7 +2971,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2980,7 +2980,7 @@
         <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3060,7 +3060,7 @@
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -3069,7 +3069,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3122,13 +3122,13 @@
         <v>5</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -3140,16 +3140,16 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -3158,7 +3158,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3182,16 +3182,16 @@
         <v>-1</v>
       </c>
       <c r="W29">
+        <v>6</v>
+      </c>
+      <c r="X29">
+        <v>6</v>
+      </c>
+      <c r="Y29">
+        <v>6</v>
+      </c>
+      <c r="Z29">
         <v>5</v>
-      </c>
-      <c r="X29">
-        <v>-1</v>
-      </c>
-      <c r="Y29">
-        <v>6</v>
-      </c>
-      <c r="Z29">
-        <v>-1</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3238,7 +3238,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3247,7 +3247,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3354,25 +3354,25 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3386,16 +3386,16 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="G3">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
       <c r="H3">
         <v>7.3</v>
@@ -3418,25 +3418,25 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>88.89</v>
+        <v>92.59</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>11.11</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3514,19 +3514,19 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3574,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3609,16 +3609,16 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3629,13 +3629,13 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
@@ -3643,19 +3643,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920331</v>
+        <v>21330051920332</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>51</v>
@@ -3669,215 +3669,15 @@
         <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920332</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920332</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920334</v>
-      </c>
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920335</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920336</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920341</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920347</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920348</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920353</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920353</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3920,13 +3720,13 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3937,30 +3737,30 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920353</v>
+        <v>21330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3968,16 +3768,16 @@
         <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3985,95 +3785,95 @@
         <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920336</v>
+        <v>21330051920137</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920341</v>
+        <v>21330051920336</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920347</v>
+        <v>21330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920348</v>
+        <v>21330051920339</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920333</v>
+        <v>21330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>108</v>
@@ -4084,13 +3884,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920137</v>
+        <v>21330051920341</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>109</v>
@@ -4101,13 +3901,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920338</v>
+        <v>21330051920342</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
         <v>110</v>
@@ -4118,13 +3918,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920339</v>
+        <v>21330051920343</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>111</v>
@@ -4135,13 +3935,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920340</v>
+        <v>21330051920344</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
@@ -4152,13 +3952,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920342</v>
+        <v>21330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>113</v>
@@ -4169,13 +3969,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920343</v>
+        <v>21330051920346</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>114</v>
@@ -4186,13 +3986,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920344</v>
+        <v>21330051920347</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>115</v>
@@ -4203,13 +4003,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920345</v>
+        <v>21330051920348</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
         <v>116</v>
@@ -4220,13 +4020,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920346</v>
+        <v>21330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>117</v>
@@ -4237,13 +4037,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920349</v>
+        <v>21330051920350</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>118</v>
@@ -4254,16 +4054,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920350</v>
+        <v>21330051920149</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4271,16 +4071,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920149</v>
+        <v>21330051920351</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4288,13 +4088,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920351</v>
+        <v>21330051920322</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>120</v>
@@ -4305,13 +4105,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920322</v>
+        <v>21330051920174</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
         <v>121</v>
@@ -4322,13 +4122,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920174</v>
+        <v>21330051920352</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
         <v>122</v>
@@ -4339,13 +4139,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920352</v>
+        <v>21330051920353</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>123</v>
@@ -4359,10 +4159,10 @@
         <v>21330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
         <v>124</v>
@@ -4378,7 +4178,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4410,16 +4210,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920334</v>
+        <v>21330051920335</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4428,21 +4228,21 @@
         <v>49</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920335</v>
+        <v>21330051920137</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4451,21 +4251,21 @@
         <v>49</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920336</v>
+        <v>21330051920347</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4474,21 +4274,21 @@
         <v>49</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920341</v>
+        <v>21330051920353</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4497,53 +4297,7 @@
         <v>49</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920347</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920348</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2APM - Estadisticos 20212.xlsx
+++ b/grupos/2APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -167,21 +167,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Morales Vallejo Jorge Luis</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
-    <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -203,124 +203,124 @@
     <t>AVELLEIRA</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARAY</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>SOL</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>HIPOLITO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>MARITZA</t>
   </si>
   <si>
     <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARAY</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>DEBORA GEORGINA</t>
@@ -897,10 +897,10 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -918,10 +918,10 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -939,13 +939,13 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -954,19 +954,19 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>7</v>
@@ -1028,13 +1028,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1043,7 +1043,7 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -1075,10 +1075,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1096,10 +1096,10 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1117,13 +1117,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1132,16 +1132,16 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>5</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>5</v>
@@ -1206,13 +1206,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1221,13 +1221,13 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1295,13 +1295,13 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1310,19 +1310,19 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA8">
         <v>9</v>
@@ -1384,13 +1384,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1399,16 +1399,16 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1473,13 +1473,13 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1488,7 +1488,7 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1497,10 +1497,10 @@
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1562,13 +1562,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1586,10 +1586,10 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1651,13 +1651,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1666,7 +1666,7 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1740,13 +1740,13 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1755,16 +1755,16 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>7</v>
@@ -1829,13 +1829,13 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1844,7 +1844,7 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1853,7 +1853,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1918,13 +1918,13 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1933,7 +1933,7 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1945,7 +1945,7 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -2007,13 +2007,13 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2022,13 +2022,13 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -2043,7 +2043,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2096,13 +2096,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2111,7 +2111,7 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2185,13 +2185,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2200,7 +2200,7 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2274,13 +2274,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2289,19 +2289,19 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2310,7 +2310,7 @@
         <v>8</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2363,13 +2363,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2378,19 +2378,19 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>7</v>
@@ -2452,13 +2452,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2467,7 +2467,7 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2541,13 +2541,13 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2556,16 +2556,16 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2577,7 +2577,7 @@
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2630,13 +2630,13 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2645,7 +2645,7 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2654,10 +2654,10 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2719,13 +2719,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -2734,7 +2734,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2755,7 +2755,7 @@
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2808,13 +2808,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -2823,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2897,13 +2897,13 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -2912,7 +2912,7 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2933,7 +2933,7 @@
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2986,13 +2986,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3001,7 +3001,7 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -3075,13 +3075,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3090,7 +3090,7 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3111,7 +3111,7 @@
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3164,13 +3164,13 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3179,19 +3179,19 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3200,7 +3200,7 @@
         <v>7</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3253,13 +3253,13 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3268,7 +3268,7 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3354,19 +3354,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>77.78</v>
+        <v>92.59</v>
       </c>
       <c r="G2">
-        <v>22.22</v>
+        <v>7.41</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -3386,19 +3386,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="G3">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -3418,65 +3418,65 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>27</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>7.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>27</v>
@@ -3494,7 +3494,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3526,7 +3526,7 @@
         <v>3.7</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3574,7 +3574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3599,86 +3599,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920331</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920332</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920332</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3720,13 +3640,13 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3737,13 +3657,13 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3751,10 +3671,10 @@
         <v>21330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>101</v>
@@ -3768,10 +3688,10 @@
         <v>21330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>102</v>
@@ -3785,10 +3705,10 @@
         <v>21330051920335</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
         <v>103</v>
@@ -3802,10 +3722,10 @@
         <v>21330051920137</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>104</v>
@@ -3819,10 +3739,10 @@
         <v>21330051920336</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
         <v>105</v>
@@ -3836,10 +3756,10 @@
         <v>21330051920338</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
         <v>106</v>
@@ -3853,10 +3773,10 @@
         <v>21330051920339</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
         <v>107</v>
@@ -3870,10 +3790,10 @@
         <v>21330051920340</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>108</v>
@@ -3887,10 +3807,10 @@
         <v>21330051920341</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>109</v>
@@ -3904,10 +3824,10 @@
         <v>21330051920342</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
         <v>110</v>
@@ -3921,10 +3841,10 @@
         <v>21330051920343</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>111</v>
@@ -3938,10 +3858,10 @@
         <v>21330051920344</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>112</v>
@@ -3955,10 +3875,10 @@
         <v>21330051920345</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
         <v>113</v>
@@ -3972,10 +3892,10 @@
         <v>21330051920346</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>114</v>
@@ -3989,10 +3909,10 @@
         <v>21330051920347</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
         <v>115</v>
@@ -4006,10 +3926,10 @@
         <v>21330051920348</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>116</v>
@@ -4023,10 +3943,10 @@
         <v>21330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>117</v>
@@ -4040,10 +3960,10 @@
         <v>21330051920350</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
         <v>118</v>
@@ -4057,10 +3977,10 @@
         <v>21330051920149</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
         <v>112</v>
@@ -4074,10 +3994,10 @@
         <v>21330051920351</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
         <v>119</v>
@@ -4091,10 +4011,10 @@
         <v>21330051920322</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
         <v>120</v>
@@ -4108,10 +4028,10 @@
         <v>21330051920174</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>121</v>
@@ -4125,10 +4045,10 @@
         <v>21330051920352</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
         <v>122</v>
@@ -4142,10 +4062,10 @@
         <v>21330051920353</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
         <v>123</v>
@@ -4159,10 +4079,10 @@
         <v>21330051920354</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
         <v>124</v>
@@ -4178,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4210,93 +4130,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920335</v>
+        <v>21330051920331</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920137</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920347</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920353</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20212.xlsx
+++ b/grupos/2APM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="125">
   <si>
     <t>Materia</t>
   </si>
@@ -167,19 +167,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Morales Vallejo Jorge Luis</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
@@ -936,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -948,16 +948,16 @@
         <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1025,7 +1025,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1037,16 +1037,16 @@
         <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>8</v>
@@ -1093,7 +1093,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1114,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -1126,10 +1126,10 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1147,10 +1147,10 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1203,7 +1203,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -1215,10 +1215,10 @@
         <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1236,7 +1236,7 @@
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -1292,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1304,16 +1304,16 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1381,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1393,10 +1393,10 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1414,7 +1414,7 @@
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>8</v>
@@ -1464,13 +1464,13 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -1482,16 +1482,16 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1559,7 +1559,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1571,10 +1571,10 @@
         <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1648,7 +1648,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>10</v>
@@ -1660,10 +1660,10 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1737,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -1749,16 +1749,16 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1770,7 +1770,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>9</v>
@@ -1826,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1838,16 +1838,16 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>7</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1859,7 +1859,7 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>8</v>
@@ -1915,7 +1915,7 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1927,16 +1927,16 @@
         <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -2004,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -2016,16 +2016,16 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2037,7 +2037,7 @@
         <v>8</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>10</v>
@@ -2093,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -2105,10 +2105,10 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2182,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -2194,16 +2194,16 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>8</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>9</v>
@@ -2271,7 +2271,7 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -2283,16 +2283,16 @@
         <v>5</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2304,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="AA19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB19">
         <v>8</v>
@@ -2360,7 +2360,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2372,16 +2372,16 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2461,10 +2461,10 @@
         <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2538,7 +2538,7 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>6</v>
@@ -2550,10 +2550,10 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2627,7 +2627,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2639,10 +2639,10 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2716,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>6</v>
@@ -2728,16 +2728,16 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>6</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2749,7 +2749,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>10</v>
@@ -2805,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2817,10 +2817,10 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2894,7 +2894,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2906,16 +2906,16 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2983,7 +2983,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2995,10 +2995,10 @@
         <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -3084,10 +3084,10 @@
         <v>9</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -3105,7 +3105,7 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>8</v>
@@ -3155,13 +3155,13 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>8</v>
@@ -3173,16 +3173,16 @@
         <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3194,7 +3194,7 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>7</v>
@@ -3250,7 +3250,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3262,10 +3262,10 @@
         <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -3354,19 +3354,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>92.59</v>
+        <v>96.3</v>
       </c>
       <c r="G2">
-        <v>7.41</v>
+        <v>3.7</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -3398,7 +3398,7 @@
         <v>3.7</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -3430,7 +3430,7 @@
         <v>3.7</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -3462,7 +3462,7 @@
         <v>3.7</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3473,10 +3473,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>27</v>
@@ -3494,7 +3494,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3505,7 +3505,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
@@ -3514,19 +3514,19 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4098,7 +4098,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4128,29 +4128,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920331</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
